--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484767_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484767_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. BERENGUER DEL VALLE</t>
+          <t>A. VAICIUNAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3308</v>
+        <v>3.0373</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7645</v>
+        <v>-0.671</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5664</v>
+        <v>3.7083</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9578</v>
+        <v>0.9627</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4797</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4376</v>
+        <v>1.6537</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7637</v>
+        <v>0.2063</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1057</v>
+        <v>-0.5596</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6581</v>
+        <v>0.7659</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1941</v>
+        <v>0.7564</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5854</v>
+        <v>-0.1315</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7795</v>
+        <v>0.8878</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5661</v>
+        <v>2.2644</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.1887</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7548</v>
+        <v>2.4531</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8635</v>
+        <v>-0.8314</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8875999999999999</v>
+        <v>-0.6886</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0241</v>
+        <v>-0.1428</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9434</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0.6415999999999999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>V. BERENGUER DEL VALLE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0394</v>
+        <v>2.9637</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4956</v>
+        <v>1.2386</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5438</v>
+        <v>1.7251</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1616</v>
+        <v>0.9578</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5182</v>
+        <v>-0.4797</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6798</v>
+        <v>1.4376</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0946</v>
+        <v>0.7637</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4117</v>
+        <v>0.1057</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5062</v>
+        <v>0.6581</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9330000000000001</v>
+        <v>0.1941</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1066</v>
+        <v>-0.5854</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1736</v>
+        <v>0.7795</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1322</v>
+        <v>0.5661</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0192</v>
+        <v>0.7548</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4814</v>
+        <v>0.4964</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4202</v>
+        <v>0.3618</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0612</v>
+        <v>0.1346</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2642</v>
+        <v>0.9434</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8678</v>
+        <v>0.3018</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6036</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VAICIUNAS</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5178</v>
+        <v>2.7659</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2169</v>
+        <v>0.9311</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7347</v>
+        <v>1.8348</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9627</v>
+        <v>0.1616</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-1.5182</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6537</v>
+        <v>1.6798</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2063</v>
+        <v>1.0946</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5596</v>
+        <v>-0.4117</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7659</v>
+        <v>1.5062</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7564</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1315</v>
+        <v>-1.1066</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8878</v>
+        <v>0.1736</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2644</v>
+        <v>1.1322</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4531</v>
+        <v>3.0192</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3509</v>
+        <v>0.2079</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2345</v>
+        <v>-0.1443</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1163</v>
+        <v>0.3522</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6415999999999999</v>
+        <v>1.2642</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.8678</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6415999999999999</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. DE YRAOLAGOTIA TELLO</t>
+          <t>J. CALERO SEVILLANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0021</v>
+        <v>2.2419</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4552</v>
+        <v>0.1269</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5469000000000001</v>
+        <v>2.1151</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6225</v>
+        <v>0.6615</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2373</v>
+        <v>0.3866</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3852</v>
+        <v>0.2749</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6153</v>
+        <v>1.3832</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4252</v>
+        <v>1.152</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1901</v>
+        <v>0.2312</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9928</v>
+        <v>-0.7217</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.188</v>
+        <v>-0.7654</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1951</v>
+        <v>0.0437</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3774</v>
+        <v>2.0757</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4531</v>
+        <v>3.0192</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4362</v>
+        <v>-0.1934</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1234</v>
+        <v>-0.3128</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3128</v>
+        <v>0.1194</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3208</v>
+        <v>-0.3018</v>
       </c>
       <c r="W5" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2262</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CALERO SEVILLANO</t>
+          <t>J. GARCIA CORBI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4701</v>
+        <v>1.8975</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3805</v>
+        <v>2.3427</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8505</v>
+        <v>-0.4452</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6615</v>
+        <v>2.3453</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3866</v>
+        <v>0.1784</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2749</v>
+        <v>2.1668</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3832</v>
+        <v>3.6406</v>
       </c>
       <c r="K6" t="n">
-        <v>1.152</v>
+        <v>1.0408</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2312</v>
+        <v>2.5997</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7217</v>
+        <v>-1.2953</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7654</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0437</v>
+        <v>-0.4329</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>3.0192</v>
+        <v>0.9435</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9653</v>
+        <v>-0.4478</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.3544</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1451</v>
+        <v>-0.0934</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GARCIA CORBI</t>
+          <t>J. DE YRAOLAGOTIA TELLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.467</v>
+        <v>1.6216</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9916</v>
+        <v>1.3393</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5246</v>
+        <v>0.2823</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3453</v>
+        <v>1.6225</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1784</v>
+        <v>1.2373</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1668</v>
+        <v>0.3852</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6406</v>
+        <v>2.6153</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0408</v>
+        <v>2.4252</v>
       </c>
       <c r="L7" t="n">
-        <v>2.5997</v>
+        <v>0.1901</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2953</v>
+        <v>-0.9928</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-1.188</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4329</v>
+        <v>0.1951</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9435</v>
+        <v>2.4531</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8783</v>
+        <v>0.0557</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7055</v>
+        <v>0.0074</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1728</v>
+        <v>0.0483</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2546</v>
+        <v>1.4063</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1259</v>
+        <v>-0.7362</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3805</v>
+        <v>2.1425</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0004</v>
@@ -1078,13 +1078,13 @@
         <v>1.3209</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1229</v>
+        <v>0.2745</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7642</v>
+        <v>-0.3745</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8871</v>
+        <v>0.649</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.358</v>
+        <v>-0.2653</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3991</v>
+        <v>-1.0223</v>
       </c>
       <c r="F10" t="n">
         <v>0.7571</v>
@@ -1234,10 +1234,10 @@
         <v>0.5661</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3579</v>
+        <v>0.7347</v>
       </c>
       <c r="T10" t="n">
-        <v>1.064</v>
+        <v>0.4407</v>
       </c>
       <c r="U10" t="n">
         <v>0.2939</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.61</v>
+        <v>-0.3891</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0366</v>
+        <v>-0.7628</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4266</v>
+        <v>0.3737</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2896</v>
@@ -1312,13 +1312,13 @@
         <v>1.1322</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2828</v>
+        <v>-0.0619</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4086</v>
+        <v>-0.1348</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1259</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0.9624</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5823</v>
+        <v>-6.1506</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.7261</v>
+        <v>-6.0827</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1438</v>
+        <v>-0.0679</v>
       </c>
       <c r="G12" t="n">
         <v>0.6860000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>2.2644</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2492</v>
+        <v>0.1825</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.117</v>
+        <v>-0.4736</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8677</v>
+        <v>0.6561</v>
       </c>
       <c r="V12" t="n">
         <v>-3.4338</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.4984</v>
+        <v>10.3801</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.927299999999999</v>
+        <v>-2.0455</v>
       </c>
       <c r="F13" t="n">
-        <v>12.4257</v>
+        <v>12.4258</v>
       </c>
       <c r="G13" t="n">
         <v>6.735799999999999</v>
@@ -1441,7 +1441,7 @@
         <v>8.441599999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>9.780499999999998</v>
+        <v>9.7805</v>
       </c>
       <c r="K13" t="n">
         <v>6.1041</v>
@@ -1453,7 +1453,7 @@
         <v>-3.045000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.810400000000001</v>
+        <v>-7.8104</v>
       </c>
       <c r="O13" t="n">
         <v>4.7652</v>
@@ -1468,13 +1468,13 @@
         <v>17.9265</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4645999999999999</v>
+        <v>0.4172</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.5547</v>
+        <v>-1.6731</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0903</v>
+        <v>2.0902</v>
       </c>
       <c r="V13" t="n">
         <v>0.3967999999999998</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. DURAN OLMOS</t>
+          <t>V. MARTIN SORIANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3641</v>
+        <v>0.1972</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5899</v>
+        <v>-0.0964</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2258</v>
+        <v>0.2937</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8272</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2191</v>
+        <v>0.281</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.6081</v>
+        <v>0.2598</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3613</v>
+        <v>0.0211</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8875</v>
+        <v>0.0211</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5262</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1885</v>
+        <v>0.5196</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1066</v>
+        <v>0.2598</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0819</v>
+        <v>0.2598</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3209</v>
+        <v>0.3774</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5096</v>
+        <v>0.3774</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1722</v>
+        <v>-0.4191</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4173</v>
+        <v>-0.1176</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7549</v>
+        <v>-0.3016</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3018</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. MARTIN SORIANO</t>
+          <t>I. DURAN OLMOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1443</v>
+        <v>0.1873</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0964</v>
+        <v>0.4925</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2408</v>
+        <v>-0.3052</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5407999999999999</v>
+        <v>-1.8272</v>
       </c>
       <c r="H16" t="n">
-        <v>0.281</v>
+        <v>-0.2191</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2598</v>
+        <v>-1.6081</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0211</v>
+        <v>0.3613</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0211</v>
+        <v>0.8875</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.5262</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5196</v>
+        <v>-2.1885</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2598</v>
+        <v>-1.1066</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2598</v>
+        <v>-1.0819</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3774</v>
+        <v>1.3209</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3774</v>
+        <v>1.5096</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.472</v>
+        <v>0.9954</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1176</v>
+        <v>0.3199</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3545</v>
+        <v>0.6755</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3018</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7093</v>
+        <v>-0.9738</v>
       </c>
       <c r="E17" t="n">
         <v>-0.7292</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0199</v>
+        <v>-0.2446</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2377</v>
@@ -1780,13 +1780,13 @@
         <v>0.7548</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1546</v>
+        <v>-0.4191</v>
       </c>
       <c r="T17" t="n">
         <v>-0.4703</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3157</v>
+        <v>0.0512</v>
       </c>
       <c r="V17" t="n">
         <v>-0.0717</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SERNEGUET GARVI</t>
+          <t>C. SEVERA LENCINA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9663</v>
+        <v>-2.2327</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2179</v>
+        <v>-2.4952</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2516</v>
+        <v>0.2624</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4705</v>
+        <v>-1.6119</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1917</v>
+        <v>-0.7873</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6622</v>
+        <v>-0.8246</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.04</v>
+        <v>-0.7931</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1684</v>
+        <v>-0.1847</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2083</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4306</v>
+        <v>-0.8187</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9767</v>
+        <v>-0.6026</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4539</v>
+        <v>-0.2162</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.4531</v>
+        <v>0.5661</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.9062</v>
+        <v>-1.1322</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4531</v>
+        <v>1.6983</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3726</v>
+        <v>-0.4926</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5966</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7761</v>
+        <v>0.0582</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5846</v>
+        <v>-0.6943</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1317</v>
+        <v>-0.019</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.547</v>
+        <v>-0.6754</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. LOPEZ-VALVERDE CARRASCO</t>
+          <t>S. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2558</v>
+        <v>-2.3007</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.12</v>
+        <v>-2.7383</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8642</v>
+        <v>0.4376</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.8232</v>
+        <v>0.7922</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6935</v>
+        <v>0.3357</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.1297</v>
+        <v>0.4564</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4774</v>
+        <v>2.4012</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3428</v>
+        <v>1.231</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1346</v>
+        <v>1.1701</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3458</v>
+        <v>-1.609</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3507</v>
+        <v>-0.8953</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9951</v>
+        <v>-0.7137</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7548</v>
+        <v>-3.3966</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0757</v>
+        <v>-5.8497</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8305</v>
+        <v>2.4531</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5826</v>
+        <v>0.3945</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1706</v>
+        <v>-0.1952</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7531</v>
+        <v>0.5897</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2301</v>
+        <v>-0.0907</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6036</v>
+        <v>0.9054</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3736</v>
+        <v>-0.9962</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. SEVERA LENCINA</t>
+          <t>P. LOPEZ-VALVERDE CARRASCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9135</v>
+        <v>-2.3797</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8849</v>
+        <v>-3.2175</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0286</v>
+        <v>0.8378</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6119</v>
+        <v>-3.8232</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7873</v>
+        <v>-1.6935</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8246</v>
+        <v>-2.1297</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7931</v>
+        <v>-1.4774</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1847</v>
+        <v>-0.3428</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-1.1346</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8187</v>
+        <v>-2.3458</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6026</v>
+        <v>-1.3507</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2162</v>
+        <v>-0.9951</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5661</v>
+        <v>0.7548</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1322</v>
+        <v>-2.0757</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6983</v>
+        <v>2.8305</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1733</v>
+        <v>0.4587</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9406</v>
+        <v>-0.268</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2327</v>
+        <v>0.7267</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6943</v>
+        <v>0.2301</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.019</v>
+        <v>0.6036</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6754</v>
+        <v>-0.3736</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. GALVEZ ARROYO</t>
+          <t>A. SERNEGUET GARVI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.955</v>
+        <v>-2.789</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1281</v>
+        <v>-2.8025</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1731</v>
+        <v>0.0135</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7922</v>
+        <v>-1.4705</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3357</v>
+        <v>0.1917</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4564</v>
+        <v>-1.6622</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4012</v>
+        <v>-0.04</v>
       </c>
       <c r="K21" t="n">
-        <v>1.231</v>
+        <v>1.1684</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1701</v>
+        <v>-1.2083</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.609</v>
+        <v>-1.4306</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8953</v>
+        <v>-0.9767</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7137</v>
+        <v>-0.4539</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.3966</v>
+        <v>-2.4531</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.8497</v>
+        <v>-4.9062</v>
       </c>
       <c r="R21" t="n">
         <v>2.4531</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2598</v>
+        <v>0.55</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.585</v>
+        <v>0.012</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3252</v>
+        <v>0.538</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0907</v>
+        <v>0.5846</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9054</v>
+        <v>2.1317</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9962</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="22">
@@ -2125,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.498299999999999</v>
+        <v>-9.498200000000001</v>
       </c>
       <c r="E22" t="n">
         <v>-12.4255</v>
@@ -2134,19 +2134,19 @@
         <v>2.9273</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.7355</v>
+        <v>-6.735499999999999</v>
       </c>
       <c r="H22" t="n">
         <v>1.7061</v>
       </c>
       <c r="I22" t="n">
-        <v>-8.441699999999999</v>
+        <v>-8.441700000000001</v>
       </c>
       <c r="J22" t="n">
         <v>3.045</v>
       </c>
       <c r="K22" t="n">
-        <v>7.810200000000001</v>
+        <v>7.8102</v>
       </c>
       <c r="L22" t="n">
         <v>-4.7652</v>
@@ -2161,7 +2161,7 @@
         <v>-3.6765</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.8305</v>
+        <v>-2.830500000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>-17.9265</v>
@@ -2170,13 +2170,13 @@
         <v>15.096</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4646</v>
+        <v>0.4647000000000002</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.0903</v>
+        <v>-2.0902</v>
       </c>
       <c r="U22" t="n">
-        <v>2.5548</v>
+        <v>2.5547</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3966000000000001</v>
